--- a/wealth_batch2_verified_contacts.xlsx
+++ b/wealth_batch2_verified_contacts.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Verified Contacts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Manual Research" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Contacts'!$A$1:$E$39</definedName>
@@ -1502,4 +1503,178 @@
   <autoFilter ref="A1:E39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1st Commercial Credit</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Trilantic North America</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Presario Ventures</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Cotton Creek Capital</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Quake Capital Partners</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DynEvolve Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Spindletop Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Keyes Capital Group</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Mako Strategies</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Altamont Capital Partners</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Sunny River Management</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Swank Investments, Inc.</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/wealth_batch2_verified_contacts.xlsx
+++ b/wealth_batch2_verified_contacts.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Verified Contacts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Manual Research" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Contacts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Notes &amp; Caveats" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Needs Manual Research" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Contacts'!$A$1:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +36,11 @@
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,14 +69,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,14 +447,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,358 +480,358 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Parthenon Capital</t>
+          <t>8VC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Matt Lentz</t>
+          <t>Alex Moore</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Principal</t>
+          <t>Partner, 8VC</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>mlentz@parthenoncapital.com</t>
+          <t>amoore@8vc.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Stafford Capital Partners</t>
+          <t>8VC</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Kurt Faulhaber</t>
+          <t>Jake Medwell</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Co-Founder and Partner</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>kurtfaulhaber@staffordcp.com</t>
+          <t>jake@8vc.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Stafford Capital Partners</t>
+          <t>Austin Growth Capital</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Andrew Laing</t>
+          <t>John Minter</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Principal, Head of Timber Performance, Reporting &amp; Risk</t>
+          <t>Founder and Managing Director</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>andrewlaing@staffordcp.com</t>
+          <t>jcm@austingrowthcapital.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TA Associates</t>
+          <t>Barton Creek Equity Partners, LLC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Roy Burns</t>
+          <t>Tommy Odonnell</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Managing Director, Co-Head Financial Services, Americas</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>rburns@ta.com</t>
+          <t>tommy@bartoncreeklending.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TA Associates</t>
+          <t>CapStream Group</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Sarah Grado</t>
+          <t>Randy Finch</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Executive Assistant</t>
+          <t>Partner and Managing Director</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>sgrado@ta.com</t>
+          <t>rfinch@capstreamgroup.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>gatekeeper</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Escalate Capital</t>
+          <t>Capstone Capital Partners (Investing)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ross Cockrell</t>
+          <t>Ray Walter</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder/Managing Director</t>
+          <t>CEO- Private Lender</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ross@escalatecapital.com</t>
+          <t>ray@capstonelending.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Escalate Capital</t>
+          <t>Capstone Capital Partners (Investing)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Kokila Lozano</t>
+          <t>Kayla Walter</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Principal</t>
+          <t>Business Owner</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>kokila@escalatecapital.com</t>
+          <t>kayla@capstonelending.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Revival Healthcare Capital</t>
+          <t>CenterGate Capital</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Rick Anderson</t>
+          <t>Jill Holup</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Chairman</t>
+          <t>Chief Financial Officer/Chief Operating Officer</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>rick@rvlhc.com</t>
+          <t>jholup@centergatecapital.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Revival Healthcare Capital</t>
+          <t>CenterGate Capital</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sam Liang</t>
+          <t>Lewis Schoenwetter</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Operating Partner</t>
+          <t>Managing Partner</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>sam@rvlhc.com</t>
+          <t>lewis@centergatecapital.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CenterGate Capital</t>
+          <t>Escalate Capital</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Jill Holup</t>
+          <t>Ross Cockrell</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Chief Financial Officer/Chief Operating Officer</t>
+          <t>Co-Founder/Managing Director</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>jholup@centergatecapital.com</t>
+          <t>ross@escalatecapital.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CenterGate Capital</t>
+          <t>Escalate Capital</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Lewis Schoenwetter</t>
+          <t>Kokila Lozano</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Managing Partner</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>lewis@centergatecapital.com</t>
+          <t>kokila@escalatecapital.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Strattam Capital</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Bob Morse</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Founding Managing Partner</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>rmorse@strattam.com</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Escalate Capital</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Larry Bradshaw</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Portfolio Management and Compliance</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>larry@escalatecapital.com</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Strattam Capital</t>
+          <t>LiveOak Venture Partners</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Sean Williams</t>
+          <t>Krishna Srinivasan</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Vice President of Finance and Chief Compliance Officer</t>
+          <t>Founding Partner</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>swilliams@strattam.com</t>
+          <t>krishna@liveoak.vc</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -832,7 +843,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Krishna Srinivasan</t>
+          <t>Venu Shamapant</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -842,579 +853,579 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>krishna@liveoak.vc</t>
+          <t>venu@liveoak.vc</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>LiveOak Venture Partners</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Venu Shamapant</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Founding Partner</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>venu@liveoak.vc</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Mike Marcantonio</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>mike@liveoak.vc</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>S3 Ventures</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Eric Engineer</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>General Partner</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>eric@s3vc.com</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>LiveOak Venture Partners</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Creighton Hicks</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>creighton@liveoak.vc</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>S3 Ventures</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Charlie Plauche</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>General Partner</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>charlie@s3vc.com</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>LiveOak Venture Partners</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Julianna Giraldo</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>julianna@liveoak.vc</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Silverton Partners</t>
+          <t>Mainstay Global</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Kip McClanahan</t>
+          <t>Tony Frey</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>General Partner</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>kip@silvertonpartners.com</t>
+          <t>tfrey@mainstay.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Barton Creek Equity Partners, LLC</t>
+          <t>Next Coast Ventures LLC</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tommy Odonnell</t>
+          <t>Michael Smerklo</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Co Founder &amp; Managing Director - Investor</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>tommy@bartoncreeklending.com</t>
+          <t>msmerklo@nextcoastventures.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CapStream Group</t>
+          <t>Next Coast Ventures LLC</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Randy Finch</t>
+          <t>Kaitlyn Debernardo</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Partner and Managing Director</t>
+          <t>Partner, COO and Head of Platform</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>rfinch@capstreamgroup.com</t>
+          <t>kdebernardo@nextcoastventures.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Trammell Ventures</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Nicole Huebner</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Chief Operating Officer</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>nhuebner@trammell.ventures</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Next Coast Ventures LLC</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Thomas Ball</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Co-Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>tball@nextcoastventures.com</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Unknown Ventures</t>
+          <t>Parthenon Capital</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>James Gall</t>
+          <t>Matt Lentz</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>james@unknown.vc</t>
+          <t>mlentz@parthenoncapital.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Serent Capital</t>
+          <t>Peak Rock Capital</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Kevin Frick</t>
+          <t>Stjohn Dunne</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Principal | Operating Partner</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>kevin.frick@serentcapital.com</t>
+          <t>dunne@peakgrowthconsulting.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Serent Capital</t>
+          <t>Peak Rock Capital</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Carlye Nelson</t>
+          <t>Michael Hornsby</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Executive Assistant</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>carlye.nelson@serentcapital.com</t>
+          <t>hornsby@peakrockcapital.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>gatekeeper</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Peak Rock Capital</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Stjohn Dunne</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Principal | Operating Partner</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>dunne@peakgrowthconsulting.com</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Ryan Fitch</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>fitch@peakrockcapital.com</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Peak Rock Capital</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Michael Hornsby</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>hornsby@peakrockcapital.com</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>John Scata</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>scata@peakrockcapital.com</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SNH Capital Partners</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Matt Gilbreath</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Chief Operating Officer</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>mgilbreath@snhcap.com</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Peak Rock Capital</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Jung Choi</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>choi@peakrockcapital.com</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SNH Capital Partners</t>
+          <t>Revival Healthcare Capital</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Jevin Sackett</t>
+          <t>Rick Anderson</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer</t>
+          <t>Chairman</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>jsackett@snhcap.com</t>
+          <t>rick@rvlhc.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Capstone Capital Partners (Investing)</t>
+          <t>Revival Healthcare Capital</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Ray Walter</t>
+          <t>Sam Liang</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CEO- Private Lender</t>
+          <t>Operating Partner</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ray@capstonelending.com</t>
+          <t>sam@rvlhc.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Capstone Capital Partners (Investing)</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Kayla Walter</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Business Owner</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>kayla@capstonelending.com</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Revival Healthcare Capital</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Lisa Rainone</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Partner Head of Fund Administration and Compliance</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>lisa@rvlhc.com</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Mainstay Global</t>
+          <t>S3 Ventures</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Tony Frey</t>
+          <t>Eric Engineer</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>General Partner</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>tfrey@mainstay.com</t>
+          <t>eric@s3vc.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Austin Growth Capital</t>
+          <t>S3 Ventures</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>John Minter</t>
+          <t>Aaron Perman</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Founder and Managing Director</t>
+          <t>General Partner</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>jcm@austingrowthcapital.com</t>
+          <t>aaron@s3vc.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>8VC</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Alex Moore</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Partner, 8VC</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>amoore@8vc.com</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>S3 Ventures</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Joe Curry</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>joe@s3vc.com</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>8VC</t>
+          <t>SNH Capital Partners</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Jake Medwell</t>
+          <t>Matt Gilbreath</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder and Partner</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>jake@8vc.com</t>
+          <t>mgilbreath@snhcap.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Sapphire Ventures</t>
+          <t>SNH Capital Partners</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Charlie Rexford</t>
+          <t>Jevin Sackett</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Chief of Staff to CEO</t>
+          <t>Founder &amp; Chief Executive Officer</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>charlie@sapphireventures.com</t>
+          <t>jsackett@snhcap.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>decision_maker+gatekeeper</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -1426,86 +1437,785 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Ralph Debernardo</t>
+          <t>Charlie Rexford</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Partner, Head of Capital Formation &amp; IR</t>
+          <t>Chief of Staff to CEO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ralph@sapphireventures.com</t>
+          <t>charlie@sapphireventures.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Next Coast Ventures LLC</t>
+          <t>Sapphire Ventures</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Michael Smerklo</t>
+          <t>Ralph Debernardo</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Co Founder &amp; Managing Director - Investor</t>
+          <t>Partner, Head of Capital Formation &amp; IR</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>msmerklo@nextcoastventures.com</t>
+          <t>ralph@sapphireventures.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>decision_maker</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Next Coast Ventures LLC</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Kaitlyn Debernardo</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Partner, COO and Head of Platform</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>kdebernardo@nextcoastventures.com</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>decision_maker</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sapphire Ventures</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Steve Abbott</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Partner Capital Markets</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>steve@sapphireventures.com</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sapphire Ventures</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Abigail Johnson</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Partner Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>abigail@sapphireventures.com</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sapphire Ventures</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Krupa Vankayala</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Partner People and HR</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>krupa@sapphireventures.com</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sapphire Ventures</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Monica Soliz</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Director Marketing</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>monica@sapphireventures.com</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sapphire Ventures</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Tori Robertson</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Senior Director Marketing</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>tori@sapphireventures.com</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Serent Capital</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Kevin Frick</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>kevin.frick@serentcapital.com</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Silverton Partners</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Mike Dodd</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>General Partner</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>mike@silvertonpartners.com</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Silverton Partners</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Kip McClanahan</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>General Partner</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>kip@silvertonpartners.com</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Silverton Partners</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Morgan Flager</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>morgan@silvertonpartners.com</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Silverton Partners</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Roger Chen</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>roger@silvertonpartners.com</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Silverton Partners</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Rob Taylor</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Operating Partner</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>rob@silvertonpartners.com</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Silverton Partners</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Alyssa Dadoly</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>CFO and Partner</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>alyssa@silvertonpartners.com</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Silverton Partners</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Matthew Saitta</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>matthew@silvertonpartners.com</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Silverton Partners</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Addie Rasche</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>addie@silvertonpartners.com</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Silverton Partners</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Kristen Dumbeck</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>kristen@silvertonpartners.com</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Stafford Capital Partners</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Andrew Laing</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Principal, Head of Timber Performance, Reporting &amp; Risk</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>andrewlaing@staffordcp.com</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Stafford Capital Partners</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Lane French</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>lanefrench@staffordcp.com</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Stafford Capital Partners</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Ashley Marlow</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>NA Regional Lead</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>ashleymarlow@staffordcp.com</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Stafford Capital Partners</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Eric Rama</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Partner Stafford Timberland</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>ericrama@staffordcp.com</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Predicted (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Strattam Capital</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Bob Morse</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Founding Managing Partner</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>rmorse@strattam.com</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Strattam Capital</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Andrew Holden</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>aholden@strattam.com</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>TA Associates</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Roy Burns</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Co-Head Financial Services, Americas</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>rburns@ta.com</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Trammell Ventures</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Nicole Huebner</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>nhuebner@trammell.ventures</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Unknown Ventures</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>James Gall</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>james@unknown.vc</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E39"/>
+  <autoFilter ref="A1:E62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Peak Rock Capital</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Stjohn Dunne's email is on peakgrowthconsulting.com, not the fund's main peakrockcapital.com domain - likely an Operating Partner tied to a portfolio company. Verify before use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Capstone Capital Partners (Investing)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Apollo only has an org literally named 'Capstone Capital Partners' (capstonelending.com, a private lending shop). You added '(Investing)' to disambiguate from another entity - confirm this is actually the fund you meant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CenterGate Capital / 8VC</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Domain is confirmed but individual employees use inconsistent email formats (both first@ and flast@ seen) - no additional contacts predicted beyond the 2 directly verified, to avoid guessing wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>All 'Predicted (unverified)' rows</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Email built by applying the company's confirmed format to a full name sourced from the company's public team/website page, cross-validated against Apollo's obfuscated record. Not confirmed deliverable by Apollo - reasonably high confidence but not a guarantee.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1531,144 +2241,144 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>1st Commercial Credit</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Trilantic North America</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Presario Ventures</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Cotton Creek Capital</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Quake Capital Partners</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>DynEvolve Capital</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Spindletop Capital</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Keyes Capital Group</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Mako Strategies</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Altamont Capital Partners</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Sunny River Management</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Swank Investments, Inc.</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>No confident match in Apollo - find domain manually, then can re-run if needed</t>
         </is>
